--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -31,25 +31,16 @@
     <t xml:space="preserve">cp</t>
   </si>
   <si>
-    <t xml:space="preserve">2403032UCQX6AD</t>
+    <t xml:space="preserve">2403154YM5V13S</t>
   </si>
   <si>
-    <t xml:space="preserve">E80722B3H355300</t>
+    <t xml:space="preserve">2403154XXR6UEU</t>
   </si>
   <si>
-    <t xml:space="preserve">CP2403020004</t>
+    <t xml:space="preserve">2403154YA7D8QX</t>
   </si>
   <si>
-    <t xml:space="preserve">2403032UFHHA05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E80722M2H856775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2403032UMC21R5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E80722J3H352023</t>
+    <t xml:space="preserve">240315549QE82W</t>
   </si>
 </sst>
 </file>
@@ -59,7 +50,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -80,11 +71,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,7 +120,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -150,119 +136,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.57"/>
@@ -283,30 +163,23 @@
       <c r="A2" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="B3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="B4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>6</v>
+      </c>
       <c r="B5" s="1"/>
     </row>
   </sheetData>
@@ -314,8 +187,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,ปกติ"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,ปกติ"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -31,16 +31,7 @@
     <t xml:space="preserve">cp</t>
   </si>
   <si>
-    <t xml:space="preserve">2403154YM5V13S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2403154XXR6UEU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2403154YA7D8QX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240315549QE82W</t>
+    <t xml:space="preserve">24031551EPVNWY</t>
   </si>
 </sst>
 </file>
@@ -159,27 +150,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>4</v>
-      </c>
       <c r="B3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>6</v>
-      </c>
       <c r="B5" s="1"/>
     </row>
   </sheetData>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t xml:space="preserve">cp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24031551EPVNWY</t>
   </si>
 </sst>
 </file>
@@ -154,9 +151,6 @@
       <c r="B3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>3</v>
-      </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -29,6 +29,15 @@
   </si>
   <si>
     <t xml:space="preserve">cp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240329BTB8A373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240329C2X8U4H1</t>
   </si>
 </sst>
 </file>
@@ -49,16 +58,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="222"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="222"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="222"/>
     </font>
   </fonts>
   <fills count="2">
@@ -130,7 +142,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.57"/>
@@ -147,7 +159,18 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>5</v>
+      </c>
       <c r="B3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -161,8 +184,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,ปกติ"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,ปกติ"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -34,10 +34,13 @@
     <t xml:space="preserve">240329BTB8A373</t>
   </si>
   <si>
-    <t xml:space="preserve">evev</t>
+    <t xml:space="preserve">E80714F3H493786 </t>
   </si>
   <si>
     <t xml:space="preserve">240329C2X8U4H1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E80714H3H189597 </t>
   </si>
 </sst>
 </file>
@@ -58,19 +61,16 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="222"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="222"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="222"/>
     </font>
   </fonts>
   <fills count="2">
@@ -115,12 +115,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -136,48 +144,156 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1"/>
+      <c r="B5" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -31,16 +31,25 @@
     <t xml:space="preserve">cp</t>
   </si>
   <si>
-    <t xml:space="preserve">240329BTB8A373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E80714F3H493786 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">240329C2X8U4H1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E80714H3H189597 </t>
+    <t xml:space="preserve">240404S3WV2T9J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BB3H133801428 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2404010041 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">240404S6D047VD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BB3H133801408 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">240404SAFEC473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BB3H133803171 </t>
   </si>
 </sst>
 </file>
@@ -61,16 +70,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="222"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="222"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="222"/>
     </font>
   </fonts>
   <fills count="2">
@@ -144,122 +156,17 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -280,17 +187,25 @@
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3"/>
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -31,25 +31,19 @@
     <t xml:space="preserve">cp</t>
   </si>
   <si>
-    <t xml:space="preserve">240404S3WV2T9J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BB3H133801428 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CP2404010041 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">240404S6D047VD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BB3H133801408 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">240404SAFEC473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BB3H133803171 </t>
+    <t xml:space="preserve">240404T4PBBR7F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E80714F3H493786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP2404020030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240404T57KF3GK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E80714H3H189597</t>
   </si>
 </sst>
 </file>
@@ -162,11 +156,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.68"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -200,12 +194,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -31,19 +31,13 @@
     <t xml:space="preserve">cp</t>
   </si>
   <si>
-    <t xml:space="preserve">240404T4PBBR7F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E80714F3H493786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CP2404020030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240404T57KF3GK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E80714H3H189597</t>
+    <t xml:space="preserve">24040507U2YC02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2404050DD47BV5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2404050QVUBDSH</t>
   </si>
 </sst>
 </file>
@@ -64,19 +58,16 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="222"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="222"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="222"/>
     </font>
   </fonts>
   <fills count="2">
@@ -155,12 +146,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="4" style="0" width="11.64"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -174,38 +166,36 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -29,15 +29,6 @@
   </si>
   <si>
     <t xml:space="preserve">cp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24040507U2YC02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2404050DD47BV5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2404050QVUBDSH</t>
   </si>
 </sst>
 </file>
@@ -146,13 +137,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="4" style="0" width="11.64"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -173,21 +163,13 @@
       <c r="B3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -10,17 +10,17 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -29,6 +29,78 @@
   </si>
   <si>
     <t xml:space="preserve">cp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FTAU01H6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X8HR260823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FU3DU9SJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X8HR229087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FX5P2139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X8HR260839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FRRYFPW5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X8HR260832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FRUKD5M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X8HR259558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FRAUE873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X8HR226950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FR578VXD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X8HR220589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FS3BEBBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X8HR228163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FSSGWDS0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X8HR229071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FRH4R0XX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X6QU054360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FRX9A7VP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN3AR17029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240505FRFAH4G0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH2A3FF0V6</t>
   </si>
 </sst>
 </file>
@@ -40,8 +112,9 @@
   </numFmts>
   <fonts count="4">
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -103,21 +176,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -138,43 +207,124 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.01"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0"/>
+    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="แผ่นงาน2" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,87 +21,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
   <si>
-    <t xml:space="preserve">sn</t>
-  </si>
-  <si>
     <t xml:space="preserve">cp</t>
   </si>
   <si>
-    <t xml:space="preserve">240505FTAU01H6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X8HR260823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FU3DU9SJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X8HR229087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FX5P2139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X8HR260839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FRRYFPW5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X8HR260832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FRUKD5M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X8HR259558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FRAUE873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X8HR226950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FR578VXD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X8HR220589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FS3BEBBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X8HR228163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FSSGWDS0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X8HR229071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FRH4R0XX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X6QU054360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FRX9A7VP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CN3AR17029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240505FRFAH4G0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TH2A3FF0V6</t>
+    <t xml:space="preserve">240606A59K7J5Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606A72NFNHQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606A9TY9F89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606A6N3HPPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606A1XDSANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606A8VR7GR6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606A59WQTSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606A60ATX21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606A96HXY8S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606A5PM05UK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2406058D69V3MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2406069N5BMMKC</t>
   </si>
 </sst>
 </file>
@@ -116,7 +78,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -206,120 +167,141 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="31.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="29.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="0"/>
+      <c r="C2" s="0"/>
+      <c r="E2" s="0"/>
+      <c r="F2" s="0"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="0"/>
+      <c r="E3" s="0"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="0"/>
+      <c r="C4" s="0"/>
+      <c r="D4" s="0"/>
+      <c r="E4" s="0"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="0"/>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="B6" s="0"/>
+      <c r="C6" s="0"/>
+      <c r="D6" s="0"/>
+      <c r="E6" s="0"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B7" s="0"/>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="B8" s="0"/>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="0"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B9" s="0"/>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+      <c r="D10" s="0"/>
+      <c r="E10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="E11" s="0"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>26</v>
-      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -330,4 +312,22 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -29,40 +29,19 @@
     <t xml:space="preserve">cp</t>
   </si>
   <si>
-    <t xml:space="preserve">240606A59K7J5Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606A72NFNHQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606A9TY9F89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606A6N3HPPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606A1XDSANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606A8VR7GR6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606A59WQTSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606A60ATX21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606A96HXY8S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606A5PM05UK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2406058D69V3MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2406069N5BMMKC</t>
+    <t xml:space="preserve">240606A002Q4CT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606B3F76NV4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606B4A1JR78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606B5E95VF6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240606AHBP3HQ4</t>
   </si>
 </sst>
 </file>
@@ -78,6 +57,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -137,7 +117,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -148,6 +128,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -167,12 +155,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H34"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="31.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="29.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -183,107 +170,127 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0"/>
-      <c r="C2" s="0"/>
-      <c r="E2" s="0"/>
-      <c r="F2" s="0"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="0"/>
-      <c r="E3" s="0"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="0"/>
-      <c r="C4" s="0"/>
-      <c r="D4" s="0"/>
-      <c r="E4" s="0"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0"/>
-      <c r="C5" s="0"/>
-      <c r="D5" s="0"/>
-      <c r="E5" s="0"/>
-      <c r="F5" s="0"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="0"/>
-      <c r="C6" s="0"/>
-      <c r="D6" s="0"/>
-      <c r="E6" s="0"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="0"/>
-      <c r="C7" s="0"/>
-      <c r="D7" s="0"/>
-      <c r="E7" s="0"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="B8" s="0"/>
       <c r="C8" s="0"/>
-      <c r="D8" s="0"/>
-      <c r="E8" s="0"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B9" s="0"/>
       <c r="C9" s="0"/>
       <c r="D9" s="0"/>
       <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="A10" s="3"/>
       <c r="B10" s="0"/>
       <c r="C10" s="0"/>
       <c r="D10" s="0"/>
       <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>11</v>
-      </c>
+      <c r="A11" s="3"/>
+      <c r="B11" s="0"/>
+      <c r="C11" s="0"/>
+      <c r="D11" s="0"/>
       <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>12</v>
-      </c>
+      <c r="A12" s="0"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>13</v>
-      </c>
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0"/>
@@ -299,9 +306,61 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0"/>
+      <c r="B18" s="0"/>
+      <c r="C18" s="0"/>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -320,7 +379,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -21,27 +21,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
   <si>
+    <t xml:space="preserve">MNL-001941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-001886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO3-000919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co3-000964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-001856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-001906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-002022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNL-001743</t>
+  </si>
+  <si>
     <t xml:space="preserve">cp</t>
   </si>
   <si>
-    <t xml:space="preserve">240606A002Q4CT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606B3F76NV4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606B4A1JR78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606B5E95VF6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240606AHBP3HQ4</t>
+    <t xml:space="preserve">240608DXNQMMFB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNC40410DG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9F50100370EZ00393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DQBLFST001329002B13000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8CC4082XH7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9T914101628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMTDPST00333512E744236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD9M024303035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLFW3P3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240608EVM1XK36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9F50100370EZ00388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMTDPST00333512F174236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240608E1XV4YA9</t>
   </si>
 </sst>
 </file>
@@ -147,6 +195,16 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -155,157 +213,209 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L51"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="29.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="C4" s="0"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="F4" s="0"/>
       <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3"/>
+      <c r="A5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
+      <c r="L5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="0"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+      <c r="B7" s="0"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0"/>
-      <c r="C8" s="0"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0"/>
-      <c r="C9" s="0"/>
-      <c r="D9" s="0"/>
-      <c r="E9" s="0"/>
-      <c r="F9" s="0"/>
-      <c r="G9" s="0"/>
-      <c r="H9" s="0"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="L9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
       <c r="B10" s="0"/>
-      <c r="C10" s="0"/>
-      <c r="D10" s="0"/>
-      <c r="E10" s="0"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
       <c r="F10" s="0"/>
       <c r="G10" s="0"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
       <c r="B11" s="0"/>
-      <c r="C11" s="0"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="L11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="B12" s="3"/>
+      <c r="B12" s="0"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="0"/>
-      <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0"/>
       <c r="B13" s="0"/>
-      <c r="C13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0"/>
+      <c r="B15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0"/>
       <c r="B18" s="0"/>
       <c r="C18" s="0"/>
       <c r="D18" s="0"/>
@@ -313,54 +423,133 @@
       <c r="F18" s="0"/>
       <c r="G18" s="0"/>
       <c r="H18" s="0"/>
+      <c r="L18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0"/>
+      <c r="B20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0"/>
+      <c r="B22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0"/>
+      <c r="B23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0"/>
+      <c r="B24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0"/>
+      <c r="B26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0"/>
+      <c r="B27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0"/>
+      <c r="B29" s="0"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0"/>
+      <c r="B30" s="0"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="0"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="0"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="0"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0"/>
+      <c r="B34" s="0"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0"/>
+      <c r="B36" s="0"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0"/>
+      <c r="B37" s="0"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0"/>
+      <c r="B38" s="0"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0"/>
+      <c r="B39" s="0"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0"/>
+      <c r="B40" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0"/>
+      <c r="B41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0"/>
+      <c r="B42" s="0"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0"/>
+      <c r="B43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0"/>
+      <c r="B44" s="0"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0"/>
+      <c r="B45" s="0"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0"/>
+      <c r="B46" s="0"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0"/>
+      <c r="B47" s="0"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0"/>
+      <c r="B48" s="0"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0"/>
+      <c r="B49" s="0"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0"/>
+      <c r="B50" s="0"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -379,7 +568,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -21,75 +21,126 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
   <si>
-    <t xml:space="preserve">MNL-001941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNL-001886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO3-000919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Co3-000964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNL-001856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNL-001906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNL-002022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNL-001743</t>
+    <t xml:space="preserve">PR5-000503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR1-000551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5-000548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR2-000550</t>
   </si>
   <si>
     <t xml:space="preserve">cp</t>
   </si>
   <si>
-    <t xml:space="preserve">240608DXNQMMFB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNC40410DG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9F50100370EZ00393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DQBLFST001329002B13000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8CC4082XH7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA9T914101628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMTDPST00333512E744236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD9M024303035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLFW3P3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240608EVM1XK36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9F50100370EZ00388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMTDPST00333512F174236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240608E1XV4YA9</t>
+    <t xml:space="preserve">240611Q5W73TKG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911366C01292AA21KPUB43363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">912313C01292AB21KPPS17616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">918747B01292AB21AGXA01182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">912315C01292AC21KPGR39676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E78352G3N756109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611Q05AYA0B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911366C01292AA21KPUB42344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">912313C01292AB21KPPS17631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">912315C01292AC21KPGR40034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611PTWEVGBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911366C01292AA21KPUB43385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">912315C01292AC21KPGR40285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611QG9NCS2Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911366C01292AA21KPUB43274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">912315C01292AC21KPGR40036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240612RRPGNPGN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911366C01292AA21KPUB43366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240612S7KQUKUY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911366C01292AA21KPUB42345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611QJ3TWSSR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911366C01292AA21KPUB43376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611Q2CAMK1K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611PU3Q6B2H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611PY7K6E5V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611Q9UCXDK7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611QN2V6RJH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240612SAEQETDY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240612RUG0KSD9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611Q951RXSU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611QUQ4A5DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611PRE80MKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240611Q1EX8F3S</t>
   </si>
 </sst>
 </file>
@@ -195,16 +246,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -213,17 +254,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="29.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="29.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1020" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -248,163 +286,176 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="0"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="F4" s="0"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="0"/>
-      <c r="F3" s="0"/>
-      <c r="G3" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="0"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="0"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="0"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="E5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="0"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="L5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0"/>
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0"/>
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0"/>
+      <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0"/>
+      <c r="A9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="L9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0"/>
+      <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="0"/>
-      <c r="G10" s="0"/>
-      <c r="H10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0"/>
+      <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="0"/>
-      <c r="E11" s="0"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="L11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0"/>
+      <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0"/>
+      <c r="A14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0"/>
+      <c r="A15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0"/>
-      <c r="D16" s="0"/>
-      <c r="E16" s="0"/>
-      <c r="F16" s="0"/>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0"/>
@@ -413,143 +464,159 @@
       <c r="E17" s="0"/>
       <c r="F17" s="0"/>
       <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="B18" s="0"/>
       <c r="C18" s="0"/>
       <c r="D18" s="0"/>
       <c r="E18" s="0"/>
       <c r="F18" s="0"/>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
-      <c r="L18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0"/>
+      <c r="A20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0"/>
+      <c r="A21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0"/>
+      <c r="A22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0"/>
-      <c r="B23" s="0"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0"/>
-      <c r="B24" s="0"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
-      <c r="B25" s="0"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0"/>
-      <c r="B26" s="0"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0"/>
-      <c r="B27" s="0"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0"/>
-      <c r="B28" s="0"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0"/>
-      <c r="B29" s="0"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0"/>
-      <c r="B30" s="0"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
-      <c r="B31" s="0"/>
+      <c r="B31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
-      <c r="B32" s="0"/>
+      <c r="B32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
-      <c r="B33" s="0"/>
+      <c r="B33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0"/>
-      <c r="B34" s="0"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0"/>
-      <c r="B36" s="0"/>
+      <c r="A36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0"/>
-      <c r="B37" s="0"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0"/>
-      <c r="B38" s="0"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0"/>
-      <c r="B39" s="0"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0"/>
-      <c r="B40" s="0"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0"/>
-      <c r="B41" s="0"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0"/>
-      <c r="B42" s="0"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0"/>
-      <c r="B43" s="0"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0"/>
-      <c r="B44" s="0"/>
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0"/>
-      <c r="B45" s="0"/>
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0"/>
-      <c r="B46" s="0"/>
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0"/>
-      <c r="B47" s="0"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0"/>
-      <c r="B48" s="0"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0"/>
-      <c r="B49" s="0"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0"/>
-      <c r="B50" s="0"/>
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0"/>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -568,7 +635,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,86 +469,6 @@
           <t>MNL-002088</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,17 +436,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>MNL-001743</t>
+          <t>MNL-001954</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>MNL-001910</t>
+          <t>MNL-002067</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>MNL-001911</t>
+          <t>PR5-000602</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -456,19 +456,173 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>MNL-001954</t>
+          <t>MNL-002066</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>MNL-002049</t>
+          <t xml:space="preserve">MNL-001959 </t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>MNL-002088</t>
-        </is>
-      </c>
+          <t>MNL-001771</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MNL-001926</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MNL-002095</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MNL-002022</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MNL-001925</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MNL-001856</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>MNL-001950</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>MNL-002051</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>MNL-002029</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>405TOQN31292</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>E80722J3H473594</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>E80722E4H459154</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>E80722L3H853324</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>E80722L3H853459</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>BA9H434400296</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -1,88 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t xml:space="preserve">orders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cp</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b val="true"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -90,49 +72,107 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -312,31 +352,943 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AD24"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="13.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16371" style="0" width="11.53"/>
+    <col width="11.53" customWidth="1" style="2" min="16371" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
+    <row r="1" ht="13.8" customHeight="1" s="3">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>cp</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IP1-000400</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PR1-000550</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PR1-000551</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>PR1-000585</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PR1-000600</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>PR1-000617</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PR2-000495</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>PR2-000572</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>PR2-000581</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PR5-000503</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>PR5-000547</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>PR5-000548</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>PR5-000582</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>PR5-000600</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>PR5-000610</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>PR5-000611</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>PR5-000612</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>PR5-000613</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>PR5-000618</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>PR5-000619</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>PR5-000625</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>PR5-000627</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>PR5-000646</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>PR5-000648</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>PR5-000650</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>PR6-000223</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>PR6-000279</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13.8" customHeight="1" s="3">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>240818JPH165EM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>XC25009951</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>918748B01292AB21AGWH12428</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>918747B01292AB21AGXA01881</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>912314C01292AB21KPGJ21181</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>914167C03292AB21AFYX06751</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>XB52022253</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>E72063M3X926686</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>918468B00992AA21NTMA656131</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CNB1S2S7YP</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CNB1Q8G63N</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>911366C01292AA21KPUB49604</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>912313C01292AB21KPGK68223</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>912315C01292AC21KPGS10870</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>913784C01292BA21AGGH44509</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>E80714G3H842518</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>XAGH203695</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>X8JVM45193</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>X8SF022754</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>X8H2026067</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>X94H013409</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>X8HS050063</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>TH45I6D16F</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>915073C01292AC21KNSG52891</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>915989C01292AC21KPMM09731</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>TH4587W2ZC</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>CN46FDZNHZ</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>E72065J3X620836</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>E74075F3N776034</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="13.8" customHeight="1" s="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>240818K9JW5C1H</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>XC25010606</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>918747B01292AB21AGXA01884</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>918468B00992AA21NTMA656133</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>911366C01292AA21KPUB49584</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>912313C01292AB21KPGK67020</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>912315C01292AC21KPGS10880</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>913784C01292BA21AGGH44774</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>E80714C4H908947</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>XAGH203714</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>X8JVM45228</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>X8SF022720</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>X8HS050067</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>915073C01292AC21KNSG52883</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>915989C01292AC21KPMM09174</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>CN46FDZQNJ</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>E74075K2N534782</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="13.8" customHeight="1" s="3">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>240819NAP7QPQA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>918747B01292AB21AGXA01969</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>918468B00992AA21NTMA656129</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>911366C01292AA21KPUB49610</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>912315C01292AC21KPGR81858</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>913784C01292BA21AGGH44521</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>E80714G3H839667</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>XAGH203679</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>X8JVM45225</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>915073C01292AC21KNSG52872</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CN46FDZRB1</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>E74075L2N539539</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="13.8" customHeight="1" s="3">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>240819NFBJJSPN</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>918468B00992AA21NTMA656132</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>911366C01292AA21KPUB49612</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>912315C01292AC21KPGS10525</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>913784C01292BA21AGGH44507</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>E80714D4H951023</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>XAGH124858</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>X8JVM45223</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>915073C01292AC21KNSG53677</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>CN46FDZQNX</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>E74075H3N831330</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="13.8" customHeight="1" s="3">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>240819NGY6CUNB</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>918468B00992AA21NTMA653844</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>911366C01292AA21KPUB49551</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>912315C01292AC21KPGR82875</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>913784C01292BA21AGGH44453</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>E80714D4H951117</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>XAGH203688</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>X8JVM45219</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>915073C01292AC21KNSG53663</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>CN46FDZR26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="13.8" customHeight="1" s="3">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>240819NHHPJ03S</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>918468B00992AA21NTMA656125</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>912315C01292AC21KPGR81861</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>XAGH119668</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>X8JVM44480</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>915073C01292AC21KNSG52874</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>CN46FDZQNP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="13.8" customHeight="1" s="3">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>240819NNBWNFS9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>918468B00992AA21NTMA656137</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>912315C01292AC21KPGR81779</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>XAGH124489</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X8JVM44957</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>915073C01292AC21KNSG52871</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>CN46FDZQPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="13.8" customHeight="1" s="3">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>240819NRFA5KWS</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>918468B00992AA21NTMA653992</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>912315C01292AC21KPGR81853</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>XAGH112637</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X8JVM44513</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="13.8" customHeight="1" s="3">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>240819NSXSAD0G</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>918468B00992AA21NTMA656143</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>912315C01292AC21KPGS11022</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>XAGH124513</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X8JVM44949</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="13.8" customHeight="1" s="3">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>240819NVANBFE1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>918468B00992AA21NTMA656155</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>912315C01292AC21KPGS10714</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>XAGH112485</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X8JVM44506</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="13.8" customHeight="1" s="3">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>240819NVE9QC9G</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>XAGH203722</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X8JVM44533</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="13.8" customHeight="1" s="3">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>240819NW24VXQW</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>XAGH204293</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X8JVM44524</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="13.8" customHeight="1" s="3">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>240819NX4WTQ25</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>XAGH126422</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X8JVM44541</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="13.8" customHeight="1" s="3">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>240819NX8EC3TK</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>XAGH203417</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X8JVM44458</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="13.8" customHeight="1" s="3">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>240819NYD3ATWH</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>XAGH203919</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X8JVM44544</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="13.8" customHeight="1" s="3">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>240819NYS2Q5V8</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>XAGH203903</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X8JVM44532</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="13.8" customHeight="1" s="3">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>240819P0A8Y9K4</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>XAGH203712</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X8JVM44523</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="13.8" customHeight="1" s="3">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>240819P0D4HYFM</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>XAGH123661</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X8JVM44497</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="13.8" customHeight="1" s="3">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>240819P1VD22U0</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>XAGH203924</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X8JVM44495</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="13.8" customHeight="1" s="3">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>240819P1XTBJNP</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>XAGH124129</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X8JVM44502</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="13.8" customHeight="1" s="3">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>240819P2M71QYS</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>XAGH203625</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X8JVM44519</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="13.8" customHeight="1" s="3">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>240819P3RPBUVN</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>XAGH203816</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="13.8" customHeight="1" s="3">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>240819P3X5U8Q7</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>XAGH203649</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BCP_27\Documents\GitHub\Python\test\tkinter_test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DC9CEE-E96E-464C-B76E-1F6E06A13217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="3825" yWindow="3885" windowWidth="24210" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,91 +25,211 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
-  <si>
-    <t xml:space="preserve">orders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240822084VQN7E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24082209F4Y8P3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220A6ESPX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220AWSH73B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220BFWARPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220BFXB57B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220C1GX606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220CRYFPH0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220E9H0ND2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220EAYR542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220EC5X041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220EWHVC6G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220HDYUW1R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220HWB25N2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220HWSB5AR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220K5T4V6W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220K5VY1UH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220MD40H5Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220PB1QA2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220PN8V4WP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220RG75X8U</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220T6GUMF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408220THPF48S</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
+  <si>
+    <t>orders</t>
+  </si>
+  <si>
+    <t>cp</t>
+  </si>
+  <si>
+    <t>240822084VQN7E</t>
+  </si>
+  <si>
+    <t>24082209F4Y8P3</t>
+  </si>
+  <si>
+    <t>2408220A6ESPX3</t>
+  </si>
+  <si>
+    <t>2408220AWSH73B</t>
+  </si>
+  <si>
+    <t>2408220BFWARPE</t>
+  </si>
+  <si>
+    <t>2408220BFXB57B</t>
+  </si>
+  <si>
+    <t>2408220C1GX606</t>
+  </si>
+  <si>
+    <t>2408220CRYFPH0</t>
+  </si>
+  <si>
+    <t>2408220E9H0ND2</t>
+  </si>
+  <si>
+    <t>2408220EAYR542</t>
+  </si>
+  <si>
+    <t>2408220EC5X041</t>
+  </si>
+  <si>
+    <t>2408220EWHVC6G</t>
+  </si>
+  <si>
+    <t>2408220HDYUW1R</t>
+  </si>
+  <si>
+    <t>2408220HWB25N2</t>
+  </si>
+  <si>
+    <t>2408220HWSB5AR</t>
+  </si>
+  <si>
+    <t>2408220K5T4V6W</t>
+  </si>
+  <si>
+    <t>2408220K5VY1UH</t>
+  </si>
+  <si>
+    <t>2408220MD40H5Y</t>
+  </si>
+  <si>
+    <t>2408220PB1QA2B</t>
+  </si>
+  <si>
+    <t>2408220PN8V4WP</t>
+  </si>
+  <si>
+    <t>2408220RG75X8U</t>
+  </si>
+  <si>
+    <t>2408220T6GUMF2</t>
+  </si>
+  <si>
+    <t>2408220THPF48S</t>
+  </si>
+  <si>
+    <t>240821UMR6TCE3</t>
+  </si>
+  <si>
+    <t>2408220T145XKY</t>
+  </si>
+  <si>
+    <t>2408220TQVT5T2</t>
+  </si>
+  <si>
+    <t>2408220W07AVXS</t>
+  </si>
+  <si>
+    <t>2408220WCTT0H3</t>
+  </si>
+  <si>
+    <t>2408220WVDJUKY</t>
+  </si>
+  <si>
+    <t>2408220WVSWYVR</t>
+  </si>
+  <si>
+    <t>2408220Y40Y10U</t>
+  </si>
+  <si>
+    <t>24082210EFXMEN</t>
+  </si>
+  <si>
+    <t>240822118VY5P5</t>
+  </si>
+  <si>
+    <t>24082211U3JPPJ</t>
+  </si>
+  <si>
+    <t>24082212GBJAMY</t>
+  </si>
+  <si>
+    <t>24082213RM0N4F</t>
+  </si>
+  <si>
+    <t>2408221622SH08</t>
+  </si>
+  <si>
+    <t>24082319KXSTDJ</t>
+  </si>
+  <si>
+    <t>2408231AB6MDGP</t>
+  </si>
+  <si>
+    <t>2408231B8CAB7J</t>
+  </si>
+  <si>
+    <t>2408231BUT4N8G</t>
+  </si>
+  <si>
+    <t>2408231C2CW040</t>
+  </si>
+  <si>
+    <t>2408231C53N8C6</t>
+  </si>
+  <si>
+    <t>2408231C66WX69</t>
+  </si>
+  <si>
+    <t>2408231CBKHUF5</t>
+  </si>
+  <si>
+    <t>2408231EJWQ4FJ</t>
+  </si>
+  <si>
+    <t>2408231JQDPNTE</t>
+  </si>
+  <si>
+    <t>2408231JVW77T8</t>
+  </si>
+  <si>
+    <t>2408231NC24X9F</t>
+  </si>
+  <si>
+    <t>2408231U18HGKX</t>
+  </si>
+  <si>
+    <t>2408231VXRUK15</t>
+  </si>
+  <si>
+    <t>2408231Y2MENAF</t>
+  </si>
+  <si>
+    <t>2408231YQTFN25</t>
+  </si>
+  <si>
+    <t>2408231YSQFNSF</t>
+  </si>
+  <si>
+    <t>24082320TS3G4M</t>
+  </si>
+  <si>
+    <t>24082321WNWWVB</t>
+  </si>
+  <si>
+    <t>24082322TSMQ40</t>
+  </si>
+  <si>
+    <t>24082323GX7S57</t>
+  </si>
+  <si>
+    <t>24082324B88W84</t>
+  </si>
+  <si>
+    <t>24082325GQ3DAT</t>
+  </si>
+  <si>
+    <t>24082325X55BVN</t>
+  </si>
+  <si>
+    <t>24082326EV5DC4</t>
+  </si>
+  <si>
+    <t>24082327XH48BU</t>
+  </si>
+  <si>
+    <t>2408232851XB4N</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,25 +238,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -144,103 +253,90 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -248,12 +344,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -282,7 +378,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -303,7 +399,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -354,7 +450,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -372,26 +468,25 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B71"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16342" style="0" width="11.57"/>
+    <col min="16342" max="16384" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -399,171 +494,358 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="4" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="5" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="6" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="7" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="8" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="9" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="10" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="11" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="12" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="13" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="14" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="15" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="16" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="17" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="18" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="19" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="20" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="21" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="22" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="23" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="24" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BCP_27\Documents\GitHub\Python\test\tkinter_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DC9CEE-E96E-464C-B76E-1F6E06A13217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6518928E-ECDD-4DB6-9683-9D0A66973D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3825" yWindow="3885" windowWidth="24210" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29190" yWindow="390" windowWidth="14670" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
   <si>
     <t>orders</t>
   </si>
@@ -33,203 +28,188 @@
     <t>cp</t>
   </si>
   <si>
-    <t>240822084VQN7E</t>
-  </si>
-  <si>
-    <t>24082209F4Y8P3</t>
-  </si>
-  <si>
-    <t>2408220A6ESPX3</t>
-  </si>
-  <si>
-    <t>2408220AWSH73B</t>
-  </si>
-  <si>
-    <t>2408220BFWARPE</t>
-  </si>
-  <si>
-    <t>2408220BFXB57B</t>
-  </si>
-  <si>
-    <t>2408220C1GX606</t>
-  </si>
-  <si>
-    <t>2408220CRYFPH0</t>
-  </si>
-  <si>
-    <t>2408220E9H0ND2</t>
-  </si>
-  <si>
-    <t>2408220EAYR542</t>
-  </si>
-  <si>
-    <t>2408220EC5X041</t>
-  </si>
-  <si>
     <t>2408220EWHVC6G</t>
   </si>
   <si>
-    <t>2408220HDYUW1R</t>
-  </si>
-  <si>
-    <t>2408220HWB25N2</t>
-  </si>
-  <si>
-    <t>2408220HWSB5AR</t>
-  </si>
-  <si>
-    <t>2408220K5T4V6W</t>
-  </si>
-  <si>
-    <t>2408220K5VY1UH</t>
-  </si>
-  <si>
-    <t>2408220MD40H5Y</t>
-  </si>
-  <si>
-    <t>2408220PB1QA2B</t>
-  </si>
-  <si>
-    <t>2408220PN8V4WP</t>
-  </si>
-  <si>
-    <t>2408220RG75X8U</t>
-  </si>
-  <si>
-    <t>2408220T6GUMF2</t>
-  </si>
-  <si>
-    <t>2408220THPF48S</t>
-  </si>
-  <si>
-    <t>240821UMR6TCE3</t>
-  </si>
-  <si>
-    <t>2408220T145XKY</t>
-  </si>
-  <si>
-    <t>2408220TQVT5T2</t>
-  </si>
-  <si>
-    <t>2408220W07AVXS</t>
-  </si>
-  <si>
-    <t>2408220WCTT0H3</t>
-  </si>
-  <si>
-    <t>2408220WVDJUKY</t>
-  </si>
-  <si>
-    <t>2408220WVSWYVR</t>
-  </si>
-  <si>
-    <t>2408220Y40Y10U</t>
-  </si>
-  <si>
-    <t>24082210EFXMEN</t>
-  </si>
-  <si>
-    <t>240822118VY5P5</t>
-  </si>
-  <si>
-    <t>24082211U3JPPJ</t>
-  </si>
-  <si>
-    <t>24082212GBJAMY</t>
-  </si>
-  <si>
-    <t>24082213RM0N4F</t>
-  </si>
-  <si>
-    <t>2408221622SH08</t>
-  </si>
-  <si>
-    <t>24082319KXSTDJ</t>
-  </si>
-  <si>
-    <t>2408231AB6MDGP</t>
-  </si>
-  <si>
-    <t>2408231B8CAB7J</t>
-  </si>
-  <si>
-    <t>2408231BUT4N8G</t>
-  </si>
-  <si>
-    <t>2408231C2CW040</t>
-  </si>
-  <si>
     <t>2408231C53N8C6</t>
   </si>
   <si>
     <t>2408231C66WX69</t>
   </si>
   <si>
-    <t>2408231CBKHUF5</t>
-  </si>
-  <si>
-    <t>2408231EJWQ4FJ</t>
-  </si>
-  <si>
-    <t>2408231JQDPNTE</t>
-  </si>
-  <si>
-    <t>2408231JVW77T8</t>
-  </si>
-  <si>
-    <t>2408231NC24X9F</t>
-  </si>
-  <si>
-    <t>2408231U18HGKX</t>
-  </si>
-  <si>
-    <t>2408231VXRUK15</t>
-  </si>
-  <si>
-    <t>2408231Y2MENAF</t>
-  </si>
-  <si>
-    <t>2408231YQTFN25</t>
-  </si>
-  <si>
-    <t>2408231YSQFNSF</t>
-  </si>
-  <si>
-    <t>24082320TS3G4M</t>
-  </si>
-  <si>
-    <t>24082321WNWWVB</t>
-  </si>
-  <si>
-    <t>24082322TSMQ40</t>
-  </si>
-  <si>
-    <t>24082323GX7S57</t>
-  </si>
-  <si>
-    <t>24082324B88W84</t>
-  </si>
-  <si>
-    <t>24082325GQ3DAT</t>
-  </si>
-  <si>
-    <t>24082325X55BVN</t>
-  </si>
-  <si>
-    <t>24082326EV5DC4</t>
-  </si>
-  <si>
     <t>24082327XH48BU</t>
   </si>
   <si>
-    <t>2408232851XB4N</t>
+    <t>24082329MXGGD5</t>
+  </si>
+  <si>
+    <t>24082329VDWMCG</t>
+  </si>
+  <si>
+    <t>2408232ANPJ4K1</t>
+  </si>
+  <si>
+    <t>2408232BQUF94H</t>
+  </si>
+  <si>
+    <t>2408232CD2HDB9</t>
+  </si>
+  <si>
+    <t>2408232CQ5SR57</t>
+  </si>
+  <si>
+    <t>2408232D8RG8FV</t>
+  </si>
+  <si>
+    <t>2408232DCS6FAC</t>
+  </si>
+  <si>
+    <t>2408232EB08U4Q</t>
+  </si>
+  <si>
+    <t>2408232EB8UMUM</t>
+  </si>
+  <si>
+    <t>2408232FM924SS</t>
+  </si>
+  <si>
+    <t>2408232FYV46F2</t>
+  </si>
+  <si>
+    <t>2408232G6SB0C2</t>
+  </si>
+  <si>
+    <t>2408232GYNP5Y0</t>
+  </si>
+  <si>
+    <t>2408232H9BJ4YR</t>
+  </si>
+  <si>
+    <t>2408232HVQFJ4T</t>
+  </si>
+  <si>
+    <t>2408232JCC698Q</t>
+  </si>
+  <si>
+    <t>2408232JVBAXX8</t>
+  </si>
+  <si>
+    <t>2408232KNSSSQP</t>
+  </si>
+  <si>
+    <t>2408232M41MT4G</t>
+  </si>
+  <si>
+    <t>2408232MB2Q84G</t>
+  </si>
+  <si>
+    <t>2408232N9AMKMT</t>
+  </si>
+  <si>
+    <t>2408232NGAT4G9</t>
+  </si>
+  <si>
+    <t>2408232NHX8FY4</t>
+  </si>
+  <si>
+    <t>2408232PAKXVH5</t>
+  </si>
+  <si>
+    <t>2408232PKVJ2AA</t>
+  </si>
+  <si>
+    <t>2408232PN7F29E</t>
+  </si>
+  <si>
+    <t>2408232Q6Q7RJK</t>
+  </si>
+  <si>
+    <t>2408232QFS5KCB</t>
+  </si>
+  <si>
+    <t>2408232QRCRUED</t>
+  </si>
+  <si>
+    <t>2408232QWPJP19</t>
+  </si>
+  <si>
+    <t>2408232QY49645</t>
+  </si>
+  <si>
+    <t>2408232R8FR94K</t>
+  </si>
+  <si>
+    <t>2408232REGDVHY</t>
+  </si>
+  <si>
+    <t>2408232S384N09</t>
+  </si>
+  <si>
+    <t>2408232SGBSAP5</t>
+  </si>
+  <si>
+    <t>2408232SJCMVQ2</t>
+  </si>
+  <si>
+    <t>2408232T29UX7M</t>
+  </si>
+  <si>
+    <t>2408232T3JWJUA</t>
+  </si>
+  <si>
+    <t>2408232TB4708J</t>
+  </si>
+  <si>
+    <t>2408232TP340P3</t>
+  </si>
+  <si>
+    <t>2408232U466R0T</t>
+  </si>
+  <si>
+    <t>2408232U98BU1G</t>
+  </si>
+  <si>
+    <t>2408232UCURW8N</t>
+  </si>
+  <si>
+    <t>2408232VQ8UMN3</t>
+  </si>
+  <si>
+    <t>2408232W7S41KQ</t>
+  </si>
+  <si>
+    <t>2408232W9DKUFY</t>
+  </si>
+  <si>
+    <t>2408232WN0KRBR</t>
+  </si>
+  <si>
+    <t>2408232WR1TJJR</t>
+  </si>
+  <si>
+    <t>2408232X3E42T3</t>
+  </si>
+  <si>
+    <t>2408232XC4NCKG</t>
+  </si>
+  <si>
+    <t>2408232XU68BB7</t>
+  </si>
+  <si>
+    <t>2408232Y33VDR6</t>
+  </si>
+  <si>
+    <t>2408232Y8ASTVY</t>
+  </si>
+  <si>
+    <t>2408232YDDWP16</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,6 +222,12 @@
       <sz val="11"/>
       <name val="Cambria"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -276,8 +262,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -285,8 +272,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{040E4ED5-A1BB-4ADB-8FBB-E8084ADF6BFF}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -480,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="16342" max="16384" width="11.5703125" customWidth="1"/>
@@ -496,17 +484,17 @@
     </row>
     <row r="2" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -516,112 +504,112 @@
     </row>
     <row r="6" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
@@ -631,107 +619,107 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -741,52 +729,52 @@
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
@@ -796,52 +784,37 @@
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BCP_27\Documents\GitHub\Python\test\tkinter_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B026C5E3-EE11-4966-A7A5-F33EF9A723AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF81FC2-93EC-4292-B285-D75DEA0798E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="14670" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,24 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="423">
   <si>
     <t>orders</t>
   </si>
   <si>
     <t>cp</t>
-  </si>
-  <si>
-    <t>2408256WXFWV81</t>
-  </si>
-  <si>
-    <t>2408256X3TMSC8</t>
-  </si>
-  <si>
-    <t>2408256Y76K91T</t>
-  </si>
-  <si>
-    <t>2408256YPMMHQC</t>
   </si>
   <si>
     <t>2408256YR9YMEK</t>
@@ -1615,3024 +1603,3008 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>5</v>
-      </c>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
     </row>
     <row r="10" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="95" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="101" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="102" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="106" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="107" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="108" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="109" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="110" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="113" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="114" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="115" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="116" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="117" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="119" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="120" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="123" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="124" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="125" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="126" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="127" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="128" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="130" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="133" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="136" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="137" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="138" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="139" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="140" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="141" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="142" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="143" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="144" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="145" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="146" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="147" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="148" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="149" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="150" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="151" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="152" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="153" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="154" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="155" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="156" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="157" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="158" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="159" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="160" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="161" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="162" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="163" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="164" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="165" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="166" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="167" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="168" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="169" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="170" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="171" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="172" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="173" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="174" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="175" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="176" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="177" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="178" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="179" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="180" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="181" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="182" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="183" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="184" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="185" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="186" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="187" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="188" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="189" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="190" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="191" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="192" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="193" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="194" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="195" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="196" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="197" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="198" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="199" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="200" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="201" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="202" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="203" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="204" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="205" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="206" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="207" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="208" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="209" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="210" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="211" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="212" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="213" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="214" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="215" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="216" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="217" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="218" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="219" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="220" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="221" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="222" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="223" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="224" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="225" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="226" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="227" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="228" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="229" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="230" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="231" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="232" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="233" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="234" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="235" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="236" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="237" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="238" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="239" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="240" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="241" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="242" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="243" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="244" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="245" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="246" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="247" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="248" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="249" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="250" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="251" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="252" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="253" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="254" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="255" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="256" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="257" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="258" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="259" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="260" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="261" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="262" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="263" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="264" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="265" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="266" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="267" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="268" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="269" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="270" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="271" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="272" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="273" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="274" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="275" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="276" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="277" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="278" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="279" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="280" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="281" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="282" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="283" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="284" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="285" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="286" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="287" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="288" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="289" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="290" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="291" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="292" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="293" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="294" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="295" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="296" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="297" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="298" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="299" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="300" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="301" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="302" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="303" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="304" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="305" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="306" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="307" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="308" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="309" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="310" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="311" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="312" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="313" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="314" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="315" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="316" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="317" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="318" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="319" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="320" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="321" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="322" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="323" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="324" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="325" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="326" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="327" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="328" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="329" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="330" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="331" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="332" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A332" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="333" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="334" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="335" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="336" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="337" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="338" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="339" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="340" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="341" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="342" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="343" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="344" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="345" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="346" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="347" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="348" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="349" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="350" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="351" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="352" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="353" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="354" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="355" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="356" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="357" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="358" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="359" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="360" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="361" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="362" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="363" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="364" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="365" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="366" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="367" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="368" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="369" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="370" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="371" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="372" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="373" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="374" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="375" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="376" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="377" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="378" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="379" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A379" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="380" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="381" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="382" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="383" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A383" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="384" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="385" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A385" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="386" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="387" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A387" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="388" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="389" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="390" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="391" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="392" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="393" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="394" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="395" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="396" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="397" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="398" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="399" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="400" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="401" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="402" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="403" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="404" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="405" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="406" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="407" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="408" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="409" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="410" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="411" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="412" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="413" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="414" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A414" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="415" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="416" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A416" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="417" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="418" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="419" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A419" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="420" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="421" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="422" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A422" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="423" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="424" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A424" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="425" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="426" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="427" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="428" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A428" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="429" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="430" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="431" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A431" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="432" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="433" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A433" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="434" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="435" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A435" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="436" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A436" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="437" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="438" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A438" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="439" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="440" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="441" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A441" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="442" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="443" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A443" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="444" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="445" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="446" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="447" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A447" s="3" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="448" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="449" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A449" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="450" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="451" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="452" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="453" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A453" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="454" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="455" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A455" s="4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="456" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A456" s="4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="457" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A457" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="458" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="459" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A459" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="460" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="461" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A461" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="462" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A462" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="463" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A463" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="464" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="465" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="466" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="467" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A467" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="468" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="469" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A469" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="470" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="471" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A471" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="472" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="473" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A473" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="474" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="475" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A475" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="476" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="477" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A477" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="478" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="479" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A479" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="480" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="481" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="482" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A482" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="483" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="484" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A484" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="485" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="486" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A486" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="487" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="488" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="489" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A489" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="490" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A490" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="491" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A491" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="492" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A492" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="493" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="494" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="495" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A495" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="496" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="497" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A497" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="498" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A498" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="499" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A499" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="500" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A500" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="501" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="502" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A502" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="503" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A503" s="4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="504" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A504" s="4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="505" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A505" s="4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="506" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="507" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A507" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="508" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A508" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="509" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="510" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A510" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="511" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="512" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A512" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="513" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="514" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A514" s="4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="515" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="516" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A516" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="517" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="518" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A518" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="519" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="520" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A520" s="4" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="521" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A521" s="4" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="522" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A522" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="523" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="524" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A524" s="4" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="525" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A525" s="4" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="526" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A526" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="527" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="528" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A528" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="529" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="530" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A530" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="531" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A531" s="4" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="532" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="533" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A533" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="534" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="535" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A535" s="4" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="536" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A536" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="537" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="538" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A538" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="539" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="540" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A540" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="541" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A541" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="542" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A542" s="4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="543" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A543" s="4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="544" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="545" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A545" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="546" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="547" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A547" s="4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="548" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A548" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="549" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="550" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A550" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="551" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="552" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A552" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="553" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="554" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A554" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="555" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A555" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="556" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A556" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="557" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A557" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="558" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="559" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A559" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="560" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="561" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A561" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="562" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="563" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A563" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="564" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="565" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A565" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="566" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A566" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="567" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A567" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="568" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A568" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="569" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A569" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="570" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="571" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A571" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="572" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="573" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A573" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="574" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="575" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A575" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="576" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A576" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="577" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A577" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="578" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A578" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="579" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A579" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="580" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="581" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A581" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="582" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A582" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="583" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="584" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A584" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="585" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="586" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A586" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="587" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="588" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A588" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="589" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="590" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A590" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="591" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="592" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A592" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="593" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="594" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A594" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="595" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="596" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A596" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="597" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A597" s="4" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="598" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="599" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A599" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="600" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="601" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A601" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="602" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="603" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A603" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="604" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="605" spans="1:1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A605" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,42 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>250904KDKK4Q8Y</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -1,37 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BCP_27\Documents\GitHub\Python\test\tkinter_test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829FBE6E-695A-40A6-A1C9-24769B06D7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="27720" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>orders</t>
+  </si>
+  <si>
+    <t>cp</t>
+  </si>
+  <si>
+    <t>250905N9E8U3HK</t>
+  </si>
+  <si>
+    <t>250905NBSPNAK6</t>
+  </si>
+  <si>
+    <t>250905NCV7XE8A</t>
+  </si>
+  <si>
+    <t>250905NEYP4FA6</t>
+  </si>
+  <si>
+    <t>250905NF04CMJY</t>
+  </si>
+  <si>
+    <t>250905NH29HFED</t>
+  </si>
+  <si>
+    <t>250905NJ080UBS</t>
+  </si>
+  <si>
+    <t>250905NJW8VFAQ</t>
+  </si>
+  <si>
+    <t>250905NKU0M6J5</t>
+  </si>
+  <si>
+    <t>250905NP87JU2V</t>
+  </si>
+  <si>
+    <t>250905NPAMTYSY</t>
+  </si>
+  <si>
+    <t>250905NQGVET34</t>
+  </si>
+  <si>
+    <t>250905NS2TRMVG</t>
+  </si>
+  <si>
+    <t>250905NS69DAHD</t>
+  </si>
+  <si>
+    <t>250905NS69DAHE</t>
+  </si>
+  <si>
+    <t>250905NUTTXX0X</t>
+  </si>
+  <si>
+    <t>250905NXK9ETFG</t>
+  </si>
+  <si>
+    <t>250905NXK9ETFH</t>
+  </si>
+  <si>
+    <t>250905NYH9V1BG</t>
+  </si>
+  <si>
+    <t>250905P06REG82</t>
+  </si>
+  <si>
+    <t>250905P0RUCFCC</t>
+  </si>
+  <si>
+    <t>250905P0RUCFCD</t>
+  </si>
+  <si>
+    <t>250905P0RUCFCE</t>
+  </si>
+  <si>
+    <t>250905P1WFDUKN</t>
+  </si>
+  <si>
+    <t>250905P1Y10STH</t>
+  </si>
+  <si>
+    <t>250905P24360YC</t>
+  </si>
+  <si>
+    <t>250905P25VAP71</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +145,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,77 +469,152 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cp</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>250904KDKK4Q8Y</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -1,136 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BCP_27\Documents\GitHub\Python\test\tkinter_test\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829FBE6E-695A-40A6-A1C9-24769B06D7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="27720" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>orders</t>
-  </si>
-  <si>
-    <t>cp</t>
-  </si>
-  <si>
-    <t>250905N9E8U3HK</t>
-  </si>
-  <si>
-    <t>250905NBSPNAK6</t>
-  </si>
-  <si>
-    <t>250905NCV7XE8A</t>
-  </si>
-  <si>
-    <t>250905NEYP4FA6</t>
-  </si>
-  <si>
-    <t>250905NF04CMJY</t>
-  </si>
-  <si>
-    <t>250905NH29HFED</t>
-  </si>
-  <si>
-    <t>250905NJ080UBS</t>
-  </si>
-  <si>
-    <t>250905NJW8VFAQ</t>
-  </si>
-  <si>
-    <t>250905NKU0M6J5</t>
-  </si>
-  <si>
-    <t>250905NP87JU2V</t>
-  </si>
-  <si>
-    <t>250905NPAMTYSY</t>
-  </si>
-  <si>
-    <t>250905NQGVET34</t>
-  </si>
-  <si>
-    <t>250905NS2TRMVG</t>
-  </si>
-  <si>
-    <t>250905NS69DAHD</t>
-  </si>
-  <si>
-    <t>250905NS69DAHE</t>
-  </si>
-  <si>
-    <t>250905NUTTXX0X</t>
-  </si>
-  <si>
-    <t>250905NXK9ETFG</t>
-  </si>
-  <si>
-    <t>250905NXK9ETFH</t>
-  </si>
-  <si>
-    <t>250905NYH9V1BG</t>
-  </si>
-  <si>
-    <t>250905P06REG82</t>
-  </si>
-  <si>
-    <t>250905P0RUCFCC</t>
-  </si>
-  <si>
-    <t>250905P0RUCFCD</t>
-  </si>
-  <si>
-    <t>250905P0RUCFCE</t>
-  </si>
-  <si>
-    <t>250905P1WFDUKN</t>
-  </si>
-  <si>
-    <t>250905P1Y10STH</t>
-  </si>
-  <si>
-    <t>250905P24360YC</t>
-  </si>
-  <si>
-    <t>250905P25VAP71</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -145,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -469,152 +420,89 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cp</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,90 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,23 +553,43 @@
       <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2509225RVVSD7K</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2509225S02V8BH</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2509225S1MDB7M</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2509225S3KCJ1J</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2509225SU5PYAT</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -587,6 +607,110 @@
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2509225UPT2PM0</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test/tkinter_test/Accel_mode.xlsx
+++ b/test/tkinter_test/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,11 @@
       <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>25092266VAASB1</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -553,43 +557,23 @@
       <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2509225RVVSD7K</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2509225S02V8BH</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2509225S1MDB7M</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2509225S3KCJ1J</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2509225SU5PYAT</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -601,116 +585,356 @@
       <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2509226CTNE0U2</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2509226DRJVYJJ</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2509225UPT2PM0</t>
+          <t>2509226E14MMB8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2509226EA7HF26</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2509226EARPAS7</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2509226ET3THR5</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2509226EUFNG62</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2509226EYFG247</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2509226F6CRBJG</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2509226F8UV4HS</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2509226FCG9636</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2509226FWEW9HG</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2509226GPF1G9T</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2509226H1MP52H</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2509226H3V4WEW</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2509226H7WTP1A</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2509226HPWJ2PA</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2509226J2HGP6H</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2509226J2S506N</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2509226JB551N3</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2509226JN6H7T9</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2509226JXD5V78</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2509226K92K321</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2509226KS6JX63</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2509226KXYJP36</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2509226MNBSTFG</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2509226MTCVPQB</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2509226N7S5XWW</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2509226NEAXR20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2509226NP10FGW</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2509226NVY5WF5</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2509226NXD07SX</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2509226P0FR9Q8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2509226P1MY4SF</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2509226P32NQ5Q</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2509226PNB9NC1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2509226Q2RFM19</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2509226RDE38FU</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2509226RMG5CH2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2509226RUVNW6W</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2509226S6VGXX0</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2509226SCMKV8Q</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2509226SEMGE6J</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2509226SFBCC4Q</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
